--- a/Ruby/watch-list-buys.xlsx
+++ b/Ruby/watch-list-buys.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,16 +488,16 @@
         <v>23.4</v>
       </c>
       <c r="E2" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="F2" t="n">
-        <v>21.1</v>
+        <v>20.3</v>
       </c>
       <c r="G2" t="n">
         <v>21.06</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.83</v>
+        <v>-11.97</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
         <v>6.5</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="G3" t="n">
         <v>6.03</v>
@@ -548,16 +548,16 @@
         <v>22.9</v>
       </c>
       <c r="E4" t="n">
-        <v>19.1</v>
+        <v>15.5</v>
       </c>
       <c r="F4" t="n">
-        <v>19.1</v>
+        <v>15.2</v>
       </c>
       <c r="G4" t="n">
         <v>20.61</v>
       </c>
       <c r="H4" t="n">
-        <v>-16.59</v>
+        <v>-32.31</v>
       </c>
     </row>
     <row r="5">
@@ -578,16 +578,16 @@
         <v>9.4</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="F5" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-17.02</v>
+        <v>-22.34</v>
       </c>
     </row>
     <row r="6">
@@ -608,16 +608,16 @@
         <v>11.6</v>
       </c>
       <c r="E6" t="n">
-        <v>9.75</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>9.65</v>
+        <v>8.5</v>
       </c>
       <c r="G6" t="n">
         <v>10.44</v>
       </c>
       <c r="H6" t="n">
-        <v>-15.95</v>
+        <v>-22.84</v>
       </c>
     </row>
     <row r="7">
@@ -668,16 +668,16 @@
         <v>4.52</v>
       </c>
       <c r="E8" t="n">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="F8" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="G8" t="n">
         <v>4.07</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.96</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="9">
@@ -698,16 +698,16 @@
         <v>2.72</v>
       </c>
       <c r="E9" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="F9" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="G9" t="n">
         <v>2.45</v>
       </c>
       <c r="H9" t="n">
-        <v>-16.91</v>
+        <v>-25.74</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +728,7 @@
         <v>31.25</v>
       </c>
       <c r="E10" t="n">
-        <v>30.75</v>
+        <v>31.25</v>
       </c>
       <c r="F10" t="n">
         <v>30.5</v>
@@ -737,97 +737,37 @@
         <v>28.12</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>TVO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="D11" t="n">
-        <v>26.5</v>
+        <v>25.75</v>
       </c>
       <c r="E11" t="n">
-        <v>25.75</v>
+        <v>22.4</v>
       </c>
       <c r="F11" t="n">
-        <v>25.5</v>
+        <v>22.4</v>
       </c>
       <c r="G11" t="n">
-        <v>23.85</v>
+        <v>23.18</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TVO</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="E12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G12" t="n">
-        <v>23.18</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-6.02</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WHART</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="G13" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
+        <v>-13.01</v>
       </c>
     </row>
   </sheetData>
